--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R54e7a318e45a4972"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rf0606905845c4ed4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R2727bdf16ef44787"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R169c97b1cd6646ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R4267e02ec06a4ec6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R547c1fc935d844b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R6810158f7d364864"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R4fe174f559ba489c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Ra0f1f55da9074492"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rca4ec9bbef3b457a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -280,7 +280,7 @@
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="78" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="60" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="64" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -299,113 +299,85 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="5" t="str">
-        <x:v>production发布目录</x:v>
+        <x:v>Deployment候选</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
-        <x:v>output/release/production</x:v>
+        <x:v>release/production/deployment.yaml</x:v>
       </x:c>
       <x:c r="C2" s="5" t="str">
-        <x:v>保存Deployment、HPA与Kustomize入口</x:v>
+        <x:v>保存业务配置与production标签</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
-        <x:v>运行kubectl kustomize</x:v>
+        <x:v>与输入Deployment结构化比较</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="5" t="str">
-        <x:v>Deployment候选</x:v>
+        <x:v>HPA候选</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
-        <x:v>output/release/production/deployment.yaml</x:v>
+        <x:v>release/production/hpa.yaml</x:v>
       </x:c>
       <x:c r="C3" s="5" t="str">
-        <x:v>保留业务配置并补环境标签</x:v>
+        <x:v>落实容量策略</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
-        <x:v>与输入spec深度比较</x:v>
+        <x:v>与autoscaling_policy.json结构化比较</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="5" t="str">
-        <x:v>HPA候选</x:v>
+        <x:v>Kustomize入口</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
-        <x:v>output/release/production/hpa.yaml</x:v>
+        <x:v>release/production/kustomization.yaml</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
-        <x:v>落实容量组策略</x:v>
+        <x:v>声明候选发布对象</x:v>
       </x:c>
       <x:c r="D4" s="5" t="str">
-        <x:v>与合同结构化比较</x:v>
+        <x:v>运行kubectl kustomize</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="str">
-        <x:v>Kustomize入口</x:v>
+        <x:v>渲染清单</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>output/release/production/kustomization.yaml</x:v>
+        <x:v>rendered.yaml</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>声明两个发布对象</x:v>
+        <x:v>供发布负责人查看客户端生成的对象</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>解析resources并执行kubectl</x:v>
+        <x:v>解析对象身份与字段</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>渲染清单</x:v>
+        <x:v>变更记录</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>output/evidence/rendered.yaml</x:v>
+        <x:v>change_record.csv</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>供发布负责人审阅客户端构建结果</x:v>
+        <x:v>记录HPA字段变化与Deployment保留状态</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
-        <x:v>解析对象身份</x:v>
+        <x:v>回查输入与候选清单</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="5" t="str">
-        <x:v>字段核对表</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="str">
-        <x:v>output/evidence/field_review.csv</x:v>
-      </x:c>
-      <x:c r="C7" s="5" t="str">
-        <x:v>汇总合同与保护检查</x:v>
-      </x:c>
-      <x:c r="D7" s="5" t="str">
-        <x:v>按check核对</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="5" t="str">
-        <x:v>发布复核</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="str">
-        <x:v>output/evidence/release_review.json</x:v>
-      </x:c>
-      <x:c r="C8" s="5" t="str">
-        <x:v>记录对象、检查状态和结论边界</x:v>
-      </x:c>
-      <x:c r="D8" s="5" t="str">
-        <x:v>读取JSON并回查清单</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="6" t="str">
-        <x:v>说明</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="str">
-        <x:v>output/README.txt</x:v>
-      </x:c>
-      <x:c r="C9" s="6" t="str">
-        <x:v>说明材料用途与READY边界</x:v>
-      </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="A7" s="6" t="str">
+        <x:v>发布说明</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>release_notes.txt</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
+        <x:v>说明材料用途与结论边界</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
         <x:v>与实际文件互证</x:v>
       </x:c>
     </x:row>
@@ -418,10 +390,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="58" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="62" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="72" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="54" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="66" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="74" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="70" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -435,12 +407,12 @@
         <x:v>正确值</x:v>
       </x:c>
       <x:c r="D1" s="8" t="str">
-        <x:v>来源与验证</x:v>
+        <x:v>来源</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="5" t="str">
-        <x:v>HPA</x:v>
+        <x:v>release/production/hpa.yaml</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
         <x:v>apiVersion</x:v>
@@ -449,12 +421,12 @@
         <x:v>autoscaling/v2</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
-        <x:v>容量策略</x:v>
+        <x:v>Kubernetes对象合同</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="5" t="str">
-        <x:v>HPA</x:v>
+        <x:v>release/production/hpa.yaml</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
         <x:v>kind</x:v>
@@ -468,10 +440,10 @@
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="5" t="str">
-        <x:v>HPA</x:v>
+        <x:v>release/production/hpa.yaml</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
-        <x:v>metadata.name与namespace</x:v>
+        <x:v>metadata.name与metadata.namespace</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
         <x:v>queue-worker与queue-platform</x:v>
@@ -482,100 +454,30 @@
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="str">
-        <x:v>HPA</x:v>
+        <x:v>release/production/hpa.yaml</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>scaleTargetRef</x:v>
+        <x:v>spec.scaleTargetRef</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
         <x:v>apps/v1、Deployment、queue-worker</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>容量策略</x:v>
+        <x:v>autoscaling_policy.json</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="5" t="str">
-        <x:v>HPA</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="str">
-        <x:v>minReplicas与maxReplicas</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="str">
-        <x:v>4与30</x:v>
-      </x:c>
-      <x:c r="D6" s="5" t="str">
-        <x:v>autoscaling_policy.json</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="5" t="str">
-        <x:v>CPU指标</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="str">
-        <x:v>averageUtilization</x:v>
-      </x:c>
-      <x:c r="C7" s="5" t="n">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D7" s="5" t="str">
-        <x:v>autoscaling_policy.json</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="5" t="str">
-        <x:v>外部指标</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="str">
-        <x:v>metric.name</x:v>
-      </x:c>
-      <x:c r="C8" s="5" t="str">
-        <x:v>queue_depth</x:v>
-      </x:c>
-      <x:c r="D8" s="5" t="str">
-        <x:v>autoscaling_policy.json</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="5" t="str">
-        <x:v>外部指标</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="str">
-        <x:v>averageValue</x:v>
-      </x:c>
-      <x:c r="C9" s="5" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D9" s="5" t="str">
-        <x:v>autoscaling_policy.json</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="5" t="str">
-        <x:v>复核结果</x:v>
-      </x:c>
-      <x:c r="B10" s="5" t="str">
-        <x:v>scope</x:v>
-      </x:c>
-      <x:c r="C10" s="5" t="str">
-        <x:v>client_render_review</x:v>
-      </x:c>
-      <x:c r="D10" s="5" t="str">
-        <x:v>客户端能力边界</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="6" t="str">
-        <x:v>复核结果</x:v>
-      </x:c>
-      <x:c r="B11" s="6" t="str">
-        <x:v>status</x:v>
-      </x:c>
-      <x:c r="C11" s="6" t="str">
-        <x:v>READY</x:v>
-      </x:c>
-      <x:c r="D11" s="6" t="str">
-        <x:v>全部checks通过</x:v>
+      <x:c r="A6" s="6" t="str">
+        <x:v>change_record.csv</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>Deployment/queue-worker的spec状态</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="str">
+        <x:v>unchanged</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>current/deployment.yaml</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -587,10 +489,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="48" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="106" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="62" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="58" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="50" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="108" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="64" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -609,10 +511,10 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="5" t="str">
-        <x:v>渲染对象</x:v>
+        <x:v>rendered.yaml</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
-        <x:v>复合身份</x:v>
+        <x:v>对象复合身份</x:v>
       </x:c>
       <x:c r="C2" s="5" t="str">
         <x:v>apps/v1Deployment queue-worker、autoscaling/v2HorizontalPodAutoscaler queue-worker</x:v>
@@ -623,10 +525,10 @@
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="5" t="str">
-        <x:v>指标</x:v>
+        <x:v>release/production/hpa.yaml</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
-        <x:v>type</x:v>
+        <x:v>spec.metrics.type</x:v>
       </x:c>
       <x:c r="C3" s="5" t="str">
         <x:v>Resource、External</x:v>
@@ -637,10 +539,10 @@
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="5" t="str">
-        <x:v>升降策略</x:v>
+        <x:v>release/production/hpa.yaml</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
-        <x:v>policy type</x:v>
+        <x:v>升降policy type</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
         <x:v>Percent、Pods</x:v>
@@ -651,10 +553,10 @@
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="str">
-        <x:v>公共标签</x:v>
+        <x:v>候选Deployment与HPA</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>键</x:v>
+        <x:v>公共标签键</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
         <x:v>platform.example/environment、platform.example/owner、platform.example/cost-center</x:v>
@@ -665,7 +567,7 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
-        <x:v>Kustomize</x:v>
+        <x:v>release/production/kustomization.yaml</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
         <x:v>resources</x:v>
@@ -686,8 +588,8 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="52" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="58" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="66" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="70" hidden="0" customWidth="1"/>
@@ -707,15 +609,15 @@
         <x:v>容差</x:v>
       </x:c>
       <x:c r="E1" s="8" t="str">
-        <x:v>来源与验证</x:v>
+        <x:v>来源</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="5" t="str">
-        <x:v>HPA</x:v>
+        <x:v>release/production/hpa.yaml</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
-        <x:v>minReplicas</x:v>
+        <x:v>spec.minReplicas</x:v>
       </x:c>
       <x:c r="C2" s="5" t="n">
         <x:v>4</x:v>
@@ -729,10 +631,10 @@
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
       <x:c r="A3" s="5" t="str">
-        <x:v>HPA</x:v>
+        <x:v>release/production/hpa.yaml</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
-        <x:v>maxReplicas</x:v>
+        <x:v>spec.maxReplicas</x:v>
       </x:c>
       <x:c r="C3" s="5" t="n">
         <x:v>30</x:v>
@@ -746,10 +648,10 @@
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="5" t="str">
-        <x:v>CPU指标</x:v>
+        <x:v>release/production/hpa.yaml</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
-        <x:v>averageUtilization</x:v>
+        <x:v>CPU averageUtilization</x:v>
       </x:c>
       <x:c r="C4" s="5" t="n">
         <x:v>65</x:v>
@@ -763,10 +665,10 @@
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="str">
-        <x:v>scaleDown</x:v>
+        <x:v>release/production/hpa.yaml</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>stabilizationWindowSeconds</x:v>
+        <x:v>scaleDown stabilizationWindowSeconds</x:v>
       </x:c>
       <x:c r="C5" s="5" t="n">
         <x:v>300</x:v>
@@ -780,10 +682,10 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>scaleUp Percent</x:v>
+        <x:v>release/production/hpa.yaml</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>value</x:v>
+        <x:v>scaleUp Percent value</x:v>
       </x:c>
       <x:c r="C6" s="5" t="n">
         <x:v>100</x:v>
@@ -797,10 +699,10 @@
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="6" t="str">
-        <x:v>scaleDown Percent</x:v>
+        <x:v>release/production/hpa.yaml</x:v>
       </x:c>
       <x:c r="B7" s="6" t="str">
-        <x:v>value</x:v>
+        <x:v>scaleDown Percent value</x:v>
       </x:c>
       <x:c r="C7" s="6" t="n">
         <x:v>25</x:v>
@@ -821,10 +723,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="36" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="82" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="92" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="64" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="94" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="70" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
@@ -863,7 +765,7 @@
         <x:v>文件注释可以变化</x:v>
       </x:c>
       <x:c r="C3" s="5" t="str">
-        <x:v>resources只引用两个目标对象</x:v>
+        <x:v>resources须引用两个目标对象</x:v>
       </x:c>
       <x:c r="D3" s="5" t="str">
         <x:v>kubectl实际构建</x:v>
@@ -874,7 +776,7 @@
         <x:v>公共标签</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
-        <x:v>可保留原有标签</x:v>
+        <x:v>可以保留原有标签</x:v>
       </x:c>
       <x:c r="C4" s="5" t="str">
         <x:v>三个合同标签不能缺失或改值</x:v>
@@ -885,30 +787,30 @@
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="str">
-        <x:v>复核说明</x:v>
+        <x:v>发布说明</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>措辞和段落可变化</x:v>
+        <x:v>措辞和段落可以变化</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
         <x:v>不能声称实际扩缩容已发生</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>人工复核与状态字段</x:v>
+        <x:v>人工阅读并回查清单</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
-        <x:v>CSV</x:v>
+        <x:v>change_record.csv</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
         <x:v>行序可以变化</x:v>
       </x:c>
       <x:c r="C6" s="6" t="str">
-        <x:v>check、status和evidence不能变化</x:v>
+        <x:v>object、field、前后值和source的含义不能变化</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
-        <x:v>按check排序比较</x:v>
+        <x:v>按object与field比较</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R547c1fc935d844b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R6810158f7d364864"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R4fe174f559ba489c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Ra0f1f55da9074492"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rca4ec9bbef3b457a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Ra4e5487065da4463"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R3147f06753fa4ce2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R09a68c93bbf74b87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R743493c886354c36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R8f2c40b808824841"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Ra4e5487065da4463"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R3147f06753fa4ce2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R09a68c93bbf74b87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R743493c886354c36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R8f2c40b808824841"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R04715e725d954238"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rb9282425b33d4abb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="R8e644f027b404cd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R9dcc3aac99b046d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R6549ba19d21443bb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -327,7 +327,7 @@
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
       <x:c r="A4" s="5" t="str">
-        <x:v>Kustomize入口</x:v>
+        <x:v>上线Kustomize入口</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
         <x:v>release/production/kustomization.yaml</x:v>
@@ -341,43 +341,113 @@
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="str">
-        <x:v>渲染清单</x:v>
+        <x:v>撤回Deployment</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>rendered.yaml</x:v>
+        <x:v>release/rollback/deployment.yaml</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>供发布负责人查看客户端生成的对象</x:v>
+        <x:v>保存当前Deployment</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>解析对象身份与字段</x:v>
+        <x:v>与输入对象结构化比较</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="5" t="str">
+        <x:v>撤回HPA</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="str">
+        <x:v>release/rollback/hpa.yaml</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="str">
+        <x:v>保存当前HPA</x:v>
+      </x:c>
+      <x:c r="D6" s="5" t="str">
+        <x:v>与输入对象结构化比较</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="5" t="str">
+        <x:v>撤回Kustomize入口</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="str">
+        <x:v>release/rollback/kustomization.yaml</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="str">
+        <x:v>声明撤回对象</x:v>
+      </x:c>
+      <x:c r="D7" s="5" t="str">
+        <x:v>运行kubectl kustomize</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="5" t="str">
+        <x:v>上线渲染清单</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="str">
+        <x:v>rendered_production.yaml</x:v>
+      </x:c>
+      <x:c r="C8" s="5" t="str">
+        <x:v>供发布负责人查看候选对象</x:v>
+      </x:c>
+      <x:c r="D8" s="5" t="str">
+        <x:v>解析对象身份与字段</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="5" t="str">
+        <x:v>撤回渲染清单</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="str">
+        <x:v>rendered_rollback.yaml</x:v>
+      </x:c>
+      <x:c r="C9" s="5" t="str">
+        <x:v>供值班负责人查看撤回对象</x:v>
+      </x:c>
+      <x:c r="D9" s="5" t="str">
+        <x:v>解析对象身份与字段</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="5" t="str">
         <x:v>变更记录</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="str">
+      <x:c r="B10" s="5" t="str">
         <x:v>change_record.csv</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="str">
+      <x:c r="C10" s="5" t="str">
         <x:v>记录HPA字段变化与Deployment保留状态</x:v>
       </x:c>
-      <x:c r="D6" s="5" t="str">
+      <x:c r="D10" s="5" t="str">
         <x:v>回查输入与候选清单</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="6" t="str">
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="5" t="str">
+        <x:v>发布计划</x:v>
+      </x:c>
+      <x:c r="B11" s="5" t="str">
+        <x:v>release_plan.yaml</x:v>
+      </x:c>
+      <x:c r="C11" s="5" t="str">
+        <x:v>记录窗口、影响面、上线、撤回和观察安排</x:v>
+      </x:c>
+      <x:c r="D11" s="5" t="str">
+        <x:v>与release_policy.json比较</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="6" t="str">
         <x:v>发布说明</x:v>
       </x:c>
-      <x:c r="B7" s="6" t="str">
+      <x:c r="B12" s="6" t="str">
         <x:v>release_notes.txt</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
-        <x:v>说明材料用途与结论边界</x:v>
-      </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="C12" s="6" t="str">
+        <x:v>说明材料用途与操作边界</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
         <x:v>与实际文件互证</x:v>
       </x:c>
     </x:row>
@@ -511,7 +581,7 @@
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
       <x:c r="A2" s="5" t="str">
-        <x:v>rendered.yaml</x:v>
+        <x:v>两份渲染清单</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
         <x:v>对象复合身份</x:v>
@@ -520,7 +590,7 @@
         <x:v>apps/v1Deployment queue-worker、autoscaling/v2HorizontalPodAutoscaler queue-worker</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
-        <x:v>集合精确匹配</x:v>
+        <x:v>分别做集合精确匹配</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
@@ -566,16 +636,58 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="6" t="str">
+      <x:c r="A6" s="5" t="str">
         <x:v>release/production/kustomization.yaml</x:v>
       </x:c>
-      <x:c r="B6" s="6" t="str">
+      <x:c r="B6" s="5" t="str">
         <x:v>resources</x:v>
       </x:c>
-      <x:c r="C6" s="6" t="str">
+      <x:c r="C6" s="5" t="str">
         <x:v>deployment.yaml、hpa.yaml</x:v>
       </x:c>
-      <x:c r="D6" s="6" t="str">
+      <x:c r="D6" s="5" t="str">
+        <x:v>集合精确匹配</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="5" t="str">
+        <x:v>release/rollback/kustomization.yaml</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="str">
+        <x:v>resources</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="str">
+        <x:v>deployment.yaml、hpa.yaml</x:v>
+      </x:c>
+      <x:c r="D7" s="5" t="str">
+        <x:v>集合精确匹配</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="5" t="str">
+        <x:v>release_plan.yaml</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="str">
+        <x:v>rollback.triggers</x:v>
+      </x:c>
+      <x:c r="C8" s="5" t="str">
+        <x:v>apply_exit_code_nonzero、hpa_condition_AbleToScale_false、hpa_condition_ScalingActive_false</x:v>
+      </x:c>
+      <x:c r="D8" s="5" t="str">
+        <x:v>集合精确匹配</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>release_plan.yaml</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>observation.metric</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str">
+        <x:v>queue_depth、cpu_utilization_percent、hpa_desired_replicas</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
         <x:v>集合精确匹配</x:v>
       </x:c>
     </x:row>
@@ -698,20 +810,71 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="6" t="str">
-        <x:v>release/production/hpa.yaml</x:v>
-      </x:c>
-      <x:c r="B7" s="6" t="str">
+      <x:c r="A7" s="5" t="str">
+        <x:v>release/production/hpa.yaml</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="str">
         <x:v>scaleDown Percent value</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="n">
+      <x:c r="C7" s="5" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="n">
+      <x:c r="D7" s="5" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
+      <x:c r="E7" s="5" t="str">
         <x:v>autoscaling_policy.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="5" t="str">
+        <x:v>release_plan.yaml</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="str">
+        <x:v>change_window.decision_wait_minutes</x:v>
+      </x:c>
+      <x:c r="C8" s="5" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D8" s="5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" s="5" t="str">
+        <x:v>release_policy.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="5" t="str">
+        <x:v>release_plan.yaml</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="str">
+        <x:v>observation.queue_depth.boundary</x:v>
+      </x:c>
+      <x:c r="C9" s="5" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D9" s="5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="5" t="str">
+        <x:v>release_policy.json</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="6" t="str">
+        <x:v>release_plan.yaml</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>observation.cpu_utilization_percent.boundary</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10" s="6" t="str">
+        <x:v>release_policy.json</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -800,17 +963,31 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="6" t="str">
+      <x:c r="A6" s="5" t="str">
         <x:v>change_record.csv</x:v>
       </x:c>
-      <x:c r="B6" s="6" t="str">
+      <x:c r="B6" s="5" t="str">
         <x:v>行序可以变化</x:v>
       </x:c>
-      <x:c r="C6" s="6" t="str">
+      <x:c r="C6" s="5" t="str">
         <x:v>object、field、前后值和source的含义不能变化</x:v>
       </x:c>
-      <x:c r="D6" s="6" t="str">
+      <x:c r="D6" s="5" t="str">
         <x:v>按object与field比较</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>release_plan.yaml</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>触发条件和观察项顺序可以变化</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
+        <x:v>命令、窗口、影响面和数值边界不能变化</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>结构化比较</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
